--- a/data/export/2026-09-29-operations.xlsx
+++ b/data/export/2026-09-29-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1515,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,25 +2506,25 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2494,7 +2534,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2582,35 +2622,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2683,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2702,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2970,3603 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-operations.xlsx
+++ b/data/export/2026-09-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>68.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1149,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1570,7 +1594,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1636,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,7 +3251,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3202,35 +3262,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3323,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3342,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3367,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3443,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3462,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,18 +3487,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3515,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,7 +3525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3495,12 +3563,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3582,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3539,7 +3607,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3550,7 +3618,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3563,60 +3631,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3702,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3712,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3755,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3689,7 +3765,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3699,40 +3775,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3826,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3836,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3856,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3879,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3889,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3843,12 +3927,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3946,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3887,7 +3971,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3898,7 +3982,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3995,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A56891D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4005,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4015,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4043,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4056,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4114,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4127,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4175,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4194,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4230,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4243,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4191,12 +4291,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4310,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4346,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4259,22 +4359,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4307,12 +4407,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4426,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4462,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4475,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4423,12 +4523,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4542,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4578,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4591,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4501,7 +4601,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4539,12 +4639,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4658,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4694,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4707,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4655,12 +4755,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4774,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,35 +4810,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4871,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4890,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4815,7 +4915,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4826,35 +4926,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4987,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5006,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4942,35 +5042,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5103,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5122,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5158,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5219,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5238,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5274,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5335,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5354,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5390,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5451,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5470,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5506,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5567,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5586,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5622,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5683,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5702,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5738,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5799,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5818,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5854,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5915,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5934,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5970,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6031,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6050,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6086,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6147,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6166,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6202,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6263,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6282,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6318,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6379,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6398,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6434,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6495,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6514,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6550,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6611,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6630,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6555,7 +6655,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6566,7 +6666,3411 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-operations.xlsx
+++ b/data/export/2026-09-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1761,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1875,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1936,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2111,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2144,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2227,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2260,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2284,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2376,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2463,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2496,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2520,17 +2556,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2540,12 +2576,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2583,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2616,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2640,29 +2680,29 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -2670,7 +2710,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2790,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3012,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3066,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3186,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3328,7 +3368,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3377,12 +3417,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3488,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3502,35 +3542,35 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3563,12 +3603,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3582,7 +3622,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3612,83 +3652,83 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3702,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3712,107 +3752,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3826,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3836,65 +3872,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3927,12 +3963,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3946,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3976,51 +4012,55 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4043,12 +4083,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4056,29 +4096,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq27（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4103,46 +4127,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4175,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4194,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4219,18 +4247,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4275,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4253,7 +4285,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4263,32 +4295,36 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4296,7 +4332,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4310,7 +4346,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4320,33 +4356,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4399,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4369,7 +4409,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4379,40 +4419,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4426,7 +4470,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4436,33 +4480,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4475,60 +4523,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4542,7 +4594,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4552,33 +4604,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4647,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4601,7 +4657,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4639,12 +4695,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4658,7 +4714,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4683,7 +4739,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4707,7 +4763,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4717,7 +4773,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4727,12 +4783,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4755,12 +4811,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4768,13 +4824,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4799,7 +4871,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4823,60 +4895,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4890,7 +4966,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4900,33 +4976,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4939,60 +5019,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56891D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5006,7 +5090,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5016,33 +5100,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5055,60 +5143,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5122,7 +5214,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5132,33 +5224,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5171,60 +5267,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5238,7 +5338,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5248,33 +5348,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5391,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5297,7 +5401,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5335,12 +5439,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5354,7 +5458,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5403,7 +5507,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5413,7 +5517,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5451,12 +5555,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5470,7 +5574,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5495,7 +5599,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5519,7 +5623,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5529,7 +5633,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5539,12 +5643,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5567,12 +5671,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5580,13 +5684,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5635,7 +5751,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A56891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5645,7 +5761,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5683,12 +5799,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5702,7 +5818,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5751,7 +5867,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5761,7 +5877,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5799,12 +5915,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5818,7 +5934,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5867,22 +5983,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5915,12 +6031,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5934,7 +6050,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5983,22 +6099,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6031,12 +6147,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6050,7 +6166,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6099,22 +6215,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6147,12 +6263,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6166,7 +6282,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6215,22 +6331,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6263,12 +6379,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6282,7 +6398,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6331,22 +6447,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6379,12 +6495,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6398,7 +6514,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6447,22 +6563,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6495,12 +6611,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6514,7 +6630,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,7 +6679,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6573,7 +6689,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6611,12 +6727,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6630,7 +6746,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6679,7 +6795,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6689,7 +6805,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6727,12 +6843,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6746,7 +6862,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6771,7 +6887,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6795,7 +6911,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6805,7 +6921,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6843,12 +6959,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6862,7 +6978,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6887,22 +7003,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6915,7 +7027,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6925,7 +7037,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6968,7 +7080,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6982,7 +7094,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7007,7 +7119,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7025,70 +7137,66 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7102,7 +7210,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7112,107 +7220,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7226,7 +7326,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7236,107 +7336,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7350,7 +7442,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7360,65 +7452,61 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7451,12 +7539,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7470,7 +7558,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7500,41 +7588,45 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7567,12 +7659,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7586,7 +7678,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7616,41 +7708,45 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7683,12 +7779,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7702,7 +7798,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7738,35 +7834,35 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7799,12 +7895,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7818,7 +7914,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7843,46 +7939,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7915,12 +8015,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7934,7 +8034,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7970,35 +8070,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8031,12 +8131,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8050,7 +8150,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8075,46 +8175,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8147,12 +8251,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8166,7 +8270,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8196,41 +8300,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8263,12 +8371,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8282,7 +8390,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8307,46 +8415,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8379,12 +8491,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8398,7 +8510,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8423,46 +8535,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8495,12 +8611,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8514,7 +8630,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8539,7 +8655,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8550,7 +8666,7 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8679,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8573,7 +8689,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8583,40 +8699,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8630,7 +8750,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8640,33 +8760,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8679,52 +8803,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8732,7 +8860,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8746,7 +8874,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8756,33 +8884,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8795,60 +8927,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8862,7 +8998,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8872,33 +9008,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8911,22 +9051,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8964,7 +9104,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8978,7 +9118,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9008,17 +9148,13 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9031,22 +9167,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9079,12 +9215,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9098,7 +9234,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9123,7 +9259,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9147,60 +9283,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9214,7 +9354,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9224,17 +9364,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9249,12 +9389,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9407,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9277,7 +9417,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9287,32 +9427,36 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9320,7 +9464,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9334,7 +9478,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9344,17 +9488,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9369,12 +9513,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9531,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9397,7 +9541,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9407,40 +9551,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9454,7 +9602,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9464,33 +9612,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9655,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9513,7 +9665,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9523,40 +9675,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9570,7 +9726,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9580,17 +9736,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9600,13 +9756,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9779,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9629,7 +9789,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9639,40 +9799,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9686,7 +9850,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9696,17 +9860,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9716,13 +9880,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9903,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9745,7 +9913,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9783,12 +9951,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9802,7 +9970,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9851,7 +10019,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9861,7 +10029,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9871,40 +10039,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9918,7 +10090,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9928,17 +10100,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9948,13 +10120,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9967,7 +10143,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -9977,7 +10153,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -9987,40 +10163,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10034,43 +10214,2563 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC81" s="2" t="inlineStr"/>
-      <c r="AD81" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-operations.xlsx
+++ b/data/export/2026-09-29-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3444,17 +3444,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9260,17 +9260,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10992,17 +10992,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11531,32 +11531,36 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11564,7 +11568,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11588,17 +11592,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11608,17 +11612,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11677,12 @@
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -11688,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11775,32 +11779,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11808,7 +11816,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11832,17 +11840,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11852,12 +11860,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11895,32 +11903,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11928,7 +11940,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11952,17 +11964,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11972,17 +11984,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12015,32 +12027,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12048,7 +12064,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12072,17 +12088,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12092,17 +12108,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12135,32 +12151,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12168,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12192,17 +12212,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12212,7 +12232,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -12222,7 +12242,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12408,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12452,17 +12472,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12656,7 +12676,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12700,17 +12720,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12854,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13176,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13210,7 +13230,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13478,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13602,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13776,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13830,7 +13850,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14106,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14176,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14200,17 +14220,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14296,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14330,7 +14350,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14420,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14444,17 +14464,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14598,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14668,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14772,7 +14792,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14896,7 +14916,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14950,7 +14970,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15036,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15060,17 +15080,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15214,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15284,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15318,7 +15338,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15462,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15532,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15556,17 +15576,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15776,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15810,7 +15830,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16000,7 +16020,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16044,17 +16064,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16322,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -16558,7 +16578,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16648,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16682,7 +16702,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16822,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16946,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16992,7 +17012,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17116,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17170,7 +17190,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17260,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17284,17 +17304,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17438,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17508,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17532,17 +17552,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17666,7 +17686,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17752,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17910,7 +17930,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17980,7 +18000,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18104,7 +18124,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18158,7 +18178,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -18282,7 +18302,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18372,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18406,7 +18426,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18620,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18654,7 +18674,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18922,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19046,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -19150,7 +19170,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19236,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19522,7 +19542,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19592,7 +19612,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19646,7 +19666,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19790,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19860,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19884,17 +19904,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20038,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20088,7 +20108,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20142,7 +20162,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20390,7 +20410,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20758,7 +20778,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20902,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21228,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21332,7 +21352,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21376,17 +21396,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21456,7 +21476,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21500,17 +21520,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -21580,7 +21600,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21624,17 +21644,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21700,7 +21720,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21820,7 +21840,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21874,7 +21894,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21960,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22064,7 +22084,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22118,7 +22138,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22208,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22232,17 +22252,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22366,7 +22386,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22486,7 +22506,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22630,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22696,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22730,7 +22750,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22874,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22974,7 +22994,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23064,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23098,7 +23118,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23222,7 +23242,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23346,7 +23366,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23614,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23738,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23908,7 +23928,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23995,32 +24015,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24028,7 +24052,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24052,17 +24076,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24072,17 +24096,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24115,32 +24139,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -24148,7 +24176,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24172,17 +24200,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24192,17 +24220,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -24235,32 +24263,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24268,7 +24300,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24292,17 +24324,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24312,17 +24344,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -24388,7 +24420,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24475,12 +24507,12 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24508,7 +24540,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24516,10 +24548,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R195" s="2" t="inlineStr"/>
-      <c r="S195" s="2" t="inlineStr"/>
-      <c r="T195" s="2" t="inlineStr"/>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V195" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24562,7 +24610,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24595,32 +24643,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24628,7 +24680,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24652,17 +24704,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24672,17 +24724,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24715,32 +24767,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24748,7 +24804,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24772,17 +24828,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24792,17 +24848,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24868,7 +24924,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24922,7 +24978,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24955,12 +25011,12 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -24988,7 +25044,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -24996,10 +25052,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R199" s="2" t="inlineStr"/>
-      <c r="S199" s="2" t="inlineStr"/>
-      <c r="T199" s="2" t="inlineStr"/>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V199" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -25042,7 +25114,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -25108,7 +25180,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25162,7 +25234,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25228,7 +25300,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25348,7 +25420,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25402,7 +25474,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25540,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25522,7 +25594,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -25588,7 +25660,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25642,7 +25714,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -25708,7 +25780,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25832,7 +25904,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25876,12 +25948,12 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
@@ -26010,7 +26082,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26320,7 +26392,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26374,7 +26446,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26516,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26488,17 +26560,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26622,7 +26694,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26746,7 +26818,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26816,7 +26888,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26865,12 +26937,12 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26940,7 +27012,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -26984,12 +27056,12 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
@@ -27238,7 +27310,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27434,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27558,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27610,7 +27682,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27752,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27724,17 +27796,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27876,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27848,12 +27920,12 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
@@ -27982,7 +28054,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -28106,7 +28178,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28354,7 +28426,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28424,7 +28496,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28478,7 +28550,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28726,7 +28798,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28796,7 +28868,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28840,17 +28912,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28974,7 +29046,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29040,7 +29112,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29084,12 +29156,12 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
@@ -29164,7 +29236,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29213,12 +29285,12 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29538,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29662,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29728,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29700,17 +29772,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -29834,7 +29906,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30082,7 +30154,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30148,7 +30220,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30210,7 +30282,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30458,7 +30530,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30654,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30648,7 +30720,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30704,12 +30776,12 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
@@ -30838,7 +30910,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31086,7 +31158,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31282,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -31334,7 +31406,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31706,7 +31778,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31902,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31954,7 +32026,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32202,7 +32274,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32326,7 +32398,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32522,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32822,7 +32894,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32892,7 +32964,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32936,12 +33008,12 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33070,7 +33142,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33194,7 +33266,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33442,7 +33514,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33512,7 +33584,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33556,17 +33628,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33690,7 +33762,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33760,7 +33832,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33809,12 +33881,12 @@
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33938,7 +34010,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34058,7 +34130,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -34128,7 +34200,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34182,7 +34254,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34324,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34296,17 +34368,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -34430,7 +34502,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34624,7 +34696,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34668,12 +34740,12 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -34926,7 +34998,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34996,7 +35068,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35040,12 +35112,12 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35174,7 +35246,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35298,7 +35370,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35546,7 +35618,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35670,7 +35742,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35740,7 +35812,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35784,17 +35856,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35864,7 +35936,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35913,12 +35985,12 @@
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36042,7 +36114,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36166,7 +36238,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -36236,7 +36308,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36290,7 +36362,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36360,7 +36432,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36404,17 +36476,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -36662,7 +36734,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36858,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36852,7 +36924,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36896,12 +36968,12 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
@@ -37026,7 +37098,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37216,7 +37288,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37260,12 +37332,12 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
@@ -37394,7 +37466,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37642,7 +37714,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37712,7 +37784,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37756,17 +37828,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37836,7 +37908,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37890,7 +37962,7 @@
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37933,24 +38005,24 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -37960,7 +38032,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38009,12 +38081,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38047,32 +38119,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38080,7 +38156,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38104,17 +38180,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38124,12 +38200,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38167,32 +38243,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -38200,7 +38280,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38224,17 +38304,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38244,17 +38324,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -38287,32 +38367,36 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38320,7 +38404,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38344,17 +38428,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38364,12 +38448,12 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
@@ -38407,32 +38491,36 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr"/>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N308" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O308" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38440,7 +38528,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38464,17 +38552,17 @@
       </c>
       <c r="X308" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA308" s="2" t="inlineStr">
@@ -38484,17 +38572,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -38560,7 +38648,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38609,12 +38697,12 @@
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38680,7 +38768,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q310" s="2" t="inlineStr">
@@ -38724,17 +38812,17 @@
       </c>
       <c r="AB310" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC310" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD310" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-operations.xlsx
+++ b/data/export/2026-09-29-operations.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10128,17 +10128,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11736,17 +11736,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12161,24 +12161,24 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12275,32 +12275,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12308,7 +12312,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12332,17 +12336,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12352,17 +12356,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12432,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12606,7 +12610,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12858,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13180,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13220,17 +13224,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13482,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13730,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13800,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -14230,7 +14234,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14300,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14668,7 +14672,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14712,17 +14716,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14796,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14916,7 +14920,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14960,17 +14964,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15094,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15342,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15780,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15954,7 +15958,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16326,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16652,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16692,17 +16696,17 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16822,7 +16826,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17070,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17140,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17314,7 +17318,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17632,7 +17636,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17752,7 +17756,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17796,17 +17800,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18004,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18124,7 +18128,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18168,17 +18172,17 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18430,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18624,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18922,7 +18926,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19174,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19670,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20112,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20152,17 +20156,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20654,7 +20658,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21286,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21410,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21658,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21898,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21964,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22004,17 +22008,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22142,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22336,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22452,7 +22456,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22496,17 +22500,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22630,7 +22634,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22696,7 +22700,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22874,7 +22878,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23068,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23490,7 +23494,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23932,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24106,7 +24110,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24478,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -24610,7 +24614,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24862,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24982,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25020,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -25044,7 +25048,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25147,32 +25151,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -25180,7 +25188,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25204,17 +25212,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25224,17 +25232,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25267,32 +25275,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25300,7 +25312,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25324,17 +25336,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25344,17 +25356,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25387,32 +25399,36 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25420,7 +25436,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25444,17 +25460,17 @@
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA202" s="2" t="inlineStr">
@@ -25464,17 +25480,17 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25556,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25660,7 +25676,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25780,7 +25796,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -26516,7 +26532,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26565,7 +26581,7 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
@@ -26888,7 +26904,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26932,17 +26948,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27186,7 +27202,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27326,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27752,7 +27768,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27806,7 +27822,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -28054,7 +28070,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28868,7 +28884,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28917,7 +28933,7 @@
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -29236,7 +29252,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29280,17 +29296,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29414,7 +29430,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -29662,7 +29678,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -29728,7 +29744,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29782,7 +29798,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -30910,7 +30926,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -31034,7 +31050,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -32026,7 +32042,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32150,7 +32166,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -33266,7 +33282,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -33390,7 +33406,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -33584,7 +33600,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33633,7 +33649,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33832,7 +33848,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33876,17 +33892,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34010,7 +34026,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34324,7 +34340,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34378,7 +34394,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35370,7 +35386,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -35494,7 +35510,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -35812,7 +35828,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35861,7 +35877,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -35936,7 +35952,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35980,17 +35996,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36114,7 +36130,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36432,7 +36448,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36486,7 +36502,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37098,7 +37114,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37590,7 +37606,7 @@
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -37714,7 +37730,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37784,7 +37800,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37833,7 +37849,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -38032,7 +38048,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38076,17 +38092,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -38280,7 +38296,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38334,7 +38350,7 @@
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -38501,12 +38517,12 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
@@ -38528,7 +38544,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38577,7 +38593,7 @@
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
@@ -38615,32 +38631,36 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr"/>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N309" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O309" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38648,7 +38668,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38672,17 +38692,17 @@
       </c>
       <c r="X309" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y309" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z309" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA309" s="2" t="inlineStr">
@@ -38692,17 +38712,17 @@
       </c>
       <c r="AB309" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -38768,7 +38788,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q310" s="2" t="inlineStr">
@@ -38822,7 +38842,7 @@
       </c>
       <c r="AD310" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
